--- a/outputs/interpretabilidad_modelo.xlsx
+++ b/outputs/interpretabilidad_modelo.xlsx
@@ -462,16 +462,16 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>60.0112676056338</v>
+        <v>59.97468354430379</v>
       </c>
       <c r="C2">
-        <v>4.745559381010756E-267</v>
+        <v>2.051178579862612E-267</v>
       </c>
       <c r="D2">
-        <v>57.96764897234998</v>
+        <v>57.93364403815164</v>
       </c>
       <c r="E2">
-        <v>62.05488623891761</v>
+        <v>62.01572305045595</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -479,16 +479,16 @@
         <v>6</v>
       </c>
       <c r="B3">
-        <v>-21879.83975369471</v>
+        <v>-21684.88753453303</v>
       </c>
       <c r="C3">
-        <v>0.02392066807263437</v>
+        <v>0.02496443821080301</v>
       </c>
       <c r="D3">
-        <v>-40859.75046563402</v>
+        <v>-40634.21056466443</v>
       </c>
       <c r="E3">
-        <v>-2899.929041755404</v>
+        <v>-2735.564504401627</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -496,16 +496,16 @@
         <v>7</v>
       </c>
       <c r="B4">
-        <v>-7206.927025113661</v>
+        <v>-7141.647998520871</v>
       </c>
       <c r="C4">
-        <v>0.02357781342866415</v>
+        <v>0.02461025114635123</v>
       </c>
       <c r="D4">
-        <v>-13443.30472141227</v>
+        <v>-13367.00635902572</v>
       </c>
       <c r="E4">
-        <v>-970.5493288150501</v>
+        <v>-916.2896380160264</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -513,16 +513,16 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>102.7520856032184</v>
+        <v>100.577922631512</v>
       </c>
       <c r="C5">
-        <v>0.05063934407986799</v>
+        <v>0.05278085378303413</v>
       </c>
       <c r="D5">
-        <v>-0.286807076937464</v>
+        <v>-1.210974287850235</v>
       </c>
       <c r="E5">
-        <v>205.7909782833744</v>
+        <v>202.3668195508742</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -530,16 +530,16 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>-1207.571809788566</v>
+        <v>-1196.931038521037</v>
       </c>
       <c r="C6">
-        <v>0.02243994405514925</v>
+        <v>0.02344003625953886</v>
       </c>
       <c r="D6">
-        <v>-2243.838883443532</v>
+        <v>-2231.6432401103</v>
       </c>
       <c r="E6">
-        <v>-171.3047361335998</v>
+        <v>-162.2188369317741</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -547,16 +547,16 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>592.8785772358259</v>
+        <v>586.9633004202778</v>
       </c>
       <c r="C7">
-        <v>0.0261736905766597</v>
+        <v>0.02728158621028817</v>
       </c>
       <c r="D7">
-        <v>70.50679081837166</v>
+        <v>66.00371037106152</v>
       </c>
       <c r="E7">
-        <v>1115.25036365328</v>
+        <v>1107.922890469494</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -564,16 +564,16 @@
         <v>11</v>
       </c>
       <c r="B8">
-        <v>-851.4191374920013</v>
+        <v>-843.7199226240964</v>
       </c>
       <c r="C8">
-        <v>0.02240739794170418</v>
+        <v>0.02340705122613649</v>
       </c>
       <c r="D8">
-        <v>-1581.879437795159</v>
+        <v>-1572.917178119492</v>
       </c>
       <c r="E8">
-        <v>-120.958837188844</v>
+        <v>-114.5226671287011</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -581,16 +581,16 @@
         <v>12</v>
       </c>
       <c r="B9">
-        <v>-413.6633050197345</v>
+        <v>-409.9820522631182</v>
       </c>
       <c r="C9">
-        <v>0.02145559261746437</v>
+        <v>0.02242715666904951</v>
       </c>
       <c r="D9">
-        <v>-766.0059735070563</v>
+        <v>-761.7712013821804</v>
       </c>
       <c r="E9">
-        <v>-61.32063653241272</v>
+        <v>-58.19290314405612</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -598,16 +598,16 @@
         <v>13</v>
       </c>
       <c r="B10">
-        <v>-196.3175033682553</v>
+        <v>-194.4648159905006</v>
       </c>
       <c r="C10">
-        <v>0.02178548750787767</v>
+        <v>0.02277153044915444</v>
       </c>
       <c r="D10">
-        <v>-363.9563858862912</v>
+        <v>-361.7544681003438</v>
       </c>
       <c r="E10">
-        <v>-28.67862085021937</v>
+        <v>-27.17516388065738</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -615,16 +615,16 @@
         <v>14</v>
       </c>
       <c r="B11">
-        <v>-92.57261281964213</v>
+        <v>-91.69827928128578</v>
       </c>
       <c r="C11">
-        <v>0.02040413025631339</v>
+        <v>0.02136050161329965</v>
       </c>
       <c r="D11">
-        <v>-170.7751742666767</v>
+        <v>-169.746174164813</v>
       </c>
       <c r="E11">
-        <v>-14.37005137260753</v>
+        <v>-13.65038439775857</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -632,16 +632,16 @@
         <v>15</v>
       </c>
       <c r="B12">
-        <v>-37.64942657091987</v>
+        <v>-37.24866064885972</v>
       </c>
       <c r="C12">
-        <v>0.03741876386314655</v>
+        <v>0.03907184775191381</v>
       </c>
       <c r="D12">
-        <v>-73.0999956265982</v>
+        <v>-72.62428348290481</v>
       </c>
       <c r="E12">
-        <v>-2.198857515241542</v>
+        <v>-1.873037814814616</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -649,16 +649,16 @@
         <v>16</v>
       </c>
       <c r="B13">
-        <v>-20.8576164464071</v>
+        <v>-20.67227846400147</v>
       </c>
       <c r="C13">
-        <v>0.008231919592870859</v>
+        <v>0.008674492780750307</v>
       </c>
       <c r="D13">
-        <v>-36.31092740530133</v>
+        <v>-36.09259337453565</v>
       </c>
       <c r="E13">
-        <v>-5.404305487512865</v>
+        <v>-5.2519635534673</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -666,16 +666,16 @@
         <v>17</v>
       </c>
       <c r="B14">
-        <v>-8.041751934603649</v>
+        <v>-7.952618459546684</v>
       </c>
       <c r="C14">
-        <v>0.03480290717699529</v>
+        <v>0.03643326853224146</v>
       </c>
       <c r="D14">
-        <v>-15.5077481590629</v>
+        <v>-15.40166607888722</v>
       </c>
       <c r="E14">
-        <v>-0.5757557101444037</v>
+        <v>-0.5035708402061472</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -683,16 +683,16 @@
         <v>18</v>
       </c>
       <c r="B15">
-        <v>-11971.90889045888</v>
+        <v>-11863.7081711499</v>
       </c>
       <c r="C15">
-        <v>0.02376993675941483</v>
+        <v>0.02480899641612121</v>
       </c>
       <c r="D15">
-        <v>-22345.88729062254</v>
+        <v>-22219.62210133566</v>
       </c>
       <c r="E15">
-        <v>-1597.930490295215</v>
+        <v>-1507.794240964153</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -700,16 +700,16 @@
         <v>19</v>
       </c>
       <c r="B16">
-        <v>-8316.651162011744</v>
+        <v>-8240.977140189487</v>
       </c>
       <c r="C16">
-        <v>0.02366859652078305</v>
+        <v>0.02470477069622849</v>
       </c>
       <c r="D16">
-        <v>-15518.01154418448</v>
+        <v>-15429.3628905855</v>
       </c>
       <c r="E16">
-        <v>-1115.290779839006</v>
+        <v>-1052.591389793474</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -717,16 +717,16 @@
         <v>20</v>
       </c>
       <c r="B17">
-        <v>46283.36892646742</v>
+        <v>45874.28875651701</v>
       </c>
       <c r="C17">
-        <v>0.02421041698445367</v>
+        <v>0.02526132685750728</v>
       </c>
       <c r="D17">
-        <v>6051.607763465174</v>
+        <v>5704.904184210594</v>
       </c>
       <c r="E17">
-        <v>86515.13008946966</v>
+        <v>86043.67332882342</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -734,16 +734,16 @@
         <v>21</v>
       </c>
       <c r="B18">
-        <v>-1216.285465580579</v>
+        <v>-1206.439233822232</v>
       </c>
       <c r="C18">
-        <v>0.05708036665229766</v>
+        <v>0.05883483463971662</v>
       </c>
       <c r="D18">
-        <v>-2469.279667582122</v>
+        <v>-2458.041059675247</v>
       </c>
       <c r="E18">
-        <v>36.70873642096376</v>
+        <v>45.16259203078357</v>
       </c>
     </row>
   </sheetData>
